--- a/T2601_APIArduinoExtentionBoard/T2601_APIArduinoExtentionBoard-BOM.xlsx
+++ b/T2601_APIArduinoExtentionBoard/T2601_APIArduinoExtentionBoard-BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a43dc3239fed0de/PCB_Perso/T2601_APIArduino/T2601_APIArduinoExtentionBoard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="511" documentId="8_{D99A6803-265B-43E3-9609-960129D8CCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0054CC7A-A341-416D-A4F9-53A8B05CA1B9}"/>
+  <xr:revisionPtr revIDLastSave="523" documentId="8_{D99A6803-265B-43E3-9609-960129D8CCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2EF279E-F6F8-4C56-95F6-72199611C26E}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{C3AD9156-7CE6-4A1E-A3FD-D08ECF380023}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="48">
   <si>
     <t>Quoi</t>
   </si>
@@ -84,9 +84,6 @@
     <t xml:space="preserve">Lien </t>
   </si>
   <si>
-    <t>Digikey</t>
-  </si>
-  <si>
     <t>Ref PCB</t>
   </si>
   <si>
@@ -165,9 +162,6 @@
     <t>SECTION</t>
   </si>
   <si>
-    <t>https://de.aliexpress.com/item/4000330409245.html?spm=a2g0o.productlist.main.6.7a9f8vp28vp26Z&amp;algo_pvid=5d570f5f-d3a5-46c6-a6f9-af9ff0e5193a&amp;pdp_ext_f=%7B%22order%22%3A%22743%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A4000330409245%7C_p_origin_prod%3A</t>
-  </si>
-  <si>
     <t>Aliexpress</t>
   </si>
   <si>
@@ -195,12 +189,6 @@
     <t>8x0,14mm2</t>
   </si>
   <si>
-    <t>3M</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/fr/products/detail/3m/3811-16-300/22532410</t>
-  </si>
-  <si>
     <t>ScrewTerminal</t>
   </si>
   <si>
@@ -208,6 +196,12 @@
   </si>
   <si>
     <t>1x8</t>
+  </si>
+  <si>
+    <t>Conrad</t>
+  </si>
+  <si>
+    <t>https://de.aliexpress.com/item/1005011642464715.html?spm=a2g0o.productlist.main.2.2346gIpMgIpM27&amp;algo_pvid=9096bc2d-b1dc-4a6d-8b9a-ccd5a0ea05ec&amp;pdp_ext_f=%7B%22order%22%3A%2237%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005011642464715%7C_p_origin_prod%3A</t>
   </si>
 </sst>
 </file>
@@ -977,7 +971,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -996,13 +990,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>1</v>
@@ -1017,7 +1011,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J2" s="12" t="s">
         <v>5</v>
@@ -1031,13 +1025,13 @@
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A3" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -1050,21 +1044,21 @@
         <v>0.84</v>
       </c>
       <c r="K3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="14" t="s">
         <v>36</v>
-      </c>
-      <c r="L3" s="14" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A4" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>4</v>
@@ -1077,21 +1071,21 @@
         <v>0.6</v>
       </c>
       <c r="K4" t="s">
-        <v>36</v>
-      </c>
-      <c r="L4" t="s">
-        <v>37</v>
+        <v>34</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A5" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
         <v>26</v>
       </c>
-      <c r="D5" t="s">
-        <v>27</v>
-      </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1104,21 +1098,21 @@
         <v>0.185</v>
       </c>
       <c r="K5" t="s">
-        <v>36</v>
-      </c>
-      <c r="L5" t="s">
-        <v>35</v>
+        <v>34</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>2</v>
@@ -1132,22 +1126,22 @@
       </c>
       <c r="J6" s="4"/>
       <c r="K6" t="s">
-        <v>36</v>
-      </c>
-      <c r="L6" t="s">
-        <v>39</v>
+        <v>34</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" s="3"/>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F7">
         <v>2</v>
@@ -1161,21 +1155,21 @@
       </c>
       <c r="J7" s="4"/>
       <c r="K7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" t="s">
         <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" t="s">
-        <v>32</v>
       </c>
       <c r="F8">
         <v>2</v>
@@ -1189,18 +1183,18 @@
       </c>
       <c r="J8" s="4"/>
       <c r="K8" t="s">
-        <v>36</v>
-      </c>
-      <c r="L8" t="s">
-        <v>41</v>
+        <v>34</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
         <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>34</v>
       </c>
       <c r="F9">
         <v>4</v>
@@ -1212,45 +1206,38 @@
       </c>
       <c r="J9" s="4"/>
       <c r="K9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
-      <c r="H10" s="2">
-        <v>1.61</v>
-      </c>
+      <c r="H10" s="2"/>
       <c r="I10" s="2">
         <f>Tableau2[[#This Row],[Qty/PCB]]*Tableau2[[#This Row],[Prix]]</f>
-        <v>1.61</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>45</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J10" s="4"/>
       <c r="K10" t="s">
-        <v>8</v>
-      </c>
-      <c r="L10" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F11">
         <v>2</v>
@@ -1262,18 +1249,18 @@
       </c>
       <c r="J11" s="4"/>
       <c r="K11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F12">
         <v>2</v>
@@ -1285,12 +1272,12 @@
       </c>
       <c r="J12" s="4"/>
       <c r="K12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2">
@@ -1299,7 +1286,7 @@
       </c>
       <c r="J13" s="4"/>
       <c r="K13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.45">
@@ -1488,7 +1475,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="8">
@@ -1504,11 +1491,11 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D38" s="21"/>
       <c r="E38" s="17"/>
@@ -1518,11 +1505,11 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D39" s="21"/>
       <c r="E39" s="17"/>
@@ -1530,11 +1517,11 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B40" s="10"/>
       <c r="C40" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D40" s="23"/>
       <c r="E40" s="24"/>
@@ -1557,10 +1544,16 @@
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="D37:F40"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="L8" r:id="rId1" display="https://de.aliexpress.com/item/1005012223211250.html?spm=a2g0o.productlist.main.1.6cc1fuyZfuyZ4a&amp;algo_pvid=b02e5ced-4b58-4c81-a5b3-570f7ad6f6a3&amp;pdp_ext_f=%7B%22order%22%3A%2257%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005012223211250%7C_p_origin_prod%3A" xr:uid="{CC50A3DA-64A9-4E13-84EF-72CBC9CA083A}"/>
+    <hyperlink ref="L3" r:id="rId2" display="https://de.aliexpress.com/item/1005005917096107.html?spm=a2g0o.productlist.main.8.888bmzgJmzgJ8W&amp;aem_p4p_detail=2026081312393314742949988849400000034531&amp;algo_pvid=595cfd43-0cfb-4f71-8b5f-498047de2454&amp;pdp_ext_f=%7B%22order%22%3A%22436%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005005917096107%7C_p_origin_prod%3A&amp;search_p4p_id=2026081312393314742949988849400000034531_2" xr:uid="{91F7BA6B-13FB-4789-91AF-BFC62936F804}"/>
+    <hyperlink ref="L4" r:id="rId3" display="https://de.aliexpress.com/item/1005007813499880.html?spm=a2g0o.productlist.main.7.888bmzgJmzgJ8W&amp;algo_pvid=595cfd43-0cfb-4f71-8b5f-498047de2454&amp;pdp_ext_f=%7B%22order%22%3A%2268%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005007813499880%7C_p_origin_prod%3A" xr:uid="{4E6D9285-898A-48BA-B547-7A7C905ACF0B}"/>
+    <hyperlink ref="L6" r:id="rId4" display="https://de.aliexpress.com/item/1005005509699672.html?spm=a2g0o.productlist.main.15.4216I4uKI4uKck&amp;algo_pvid=73a202d8-b478-4cc9-b3c4-eb32f571c339&amp;pdp_ext_f=%7B%22order%22%3A%22758%22%2C%22spu_best_type%22%3A%22price%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005005509699672%7C_p_origin_prod%3A" xr:uid="{F7F1C5B1-8182-412E-AC7E-87A71913CE11}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>